--- a/2 digit.xlsx
+++ b/2 digit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B0985A-B5FC-4B3C-8598-ABAEB4317B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7340C513-7A17-4BF0-87DF-196F1B08993D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="190">
   <si>
     <t>SIC_2digit</t>
   </si>
   <si>
-    <t>Description</t>
-  </si>
-  <si>
     <t>01</t>
   </si>
   <si>
@@ -527,6 +524,72 @@
   </si>
   <si>
     <t>SIC_1digit</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>Description_1</t>
+  </si>
+  <si>
+    <t>Description_2</t>
+  </si>
+  <si>
+    <t>Agriculture, Forestry, And Fishing</t>
+  </si>
+  <si>
+    <t>Mining</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>Manufacturing</t>
+  </si>
+  <si>
+    <t>Transportation, Communications, Electric, Gas, And Sanitary Services</t>
+  </si>
+  <si>
+    <t>Wholesale Trade</t>
+  </si>
+  <si>
+    <t>Retail Trade</t>
+  </si>
+  <si>
+    <t>Finance, Insurance, And Real Estate</t>
+  </si>
+  <si>
+    <t>Services</t>
+  </si>
+  <si>
+    <t>Public Administration</t>
   </si>
 </sst>
 </file>
@@ -585,16 +648,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -899,937 +965,1190 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C84"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="9.06640625" style="3"/>
+    <col min="2" max="2" width="9.06640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="D5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="D6" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="D7" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>169</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="D8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>169</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9">
-        <v>2</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="D9" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A10">
-        <v>2</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="D10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A11">
-        <v>3</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="D11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>170</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A12">
-        <v>3</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="D12" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>170</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A13">
-        <v>3</v>
-      </c>
-      <c r="B13" s="3" t="s">
+      <c r="D13" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>171</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C14" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A14">
-        <v>4</v>
-      </c>
-      <c r="B14" s="3" t="s">
+      <c r="D14" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>171</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C15" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A15">
-        <v>4</v>
-      </c>
-      <c r="B15" s="3" t="s">
+      <c r="D15" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>171</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C16" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A16">
-        <v>4</v>
-      </c>
-      <c r="B16" s="3" t="s">
+      <c r="D16" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>171</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C17" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A17">
-        <v>4</v>
-      </c>
-      <c r="B17" s="3" t="s">
+      <c r="D17" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>171</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C18" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A18">
-        <v>4</v>
-      </c>
-      <c r="B18" s="3" t="s">
+      <c r="D18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>171</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C19" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A19">
-        <v>4</v>
-      </c>
-      <c r="B19" s="3" t="s">
+      <c r="D19" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>171</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C20" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A20">
-        <v>4</v>
-      </c>
-      <c r="B20" s="3" t="s">
+      <c r="D20" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>171</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C21" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A21">
-        <v>4</v>
-      </c>
-      <c r="B21" s="3" t="s">
+      <c r="D21" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>171</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C22" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A22">
-        <v>4</v>
-      </c>
-      <c r="B22" s="3" t="s">
+      <c r="D22" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>171</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C23" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A23">
-        <v>4</v>
-      </c>
-      <c r="B23" s="3" t="s">
+      <c r="D23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>171</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C24" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A24">
-        <v>4</v>
-      </c>
-      <c r="B24" s="3" t="s">
+      <c r="D24" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>171</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C25" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A25">
-        <v>4</v>
-      </c>
-      <c r="B25" s="3" t="s">
+      <c r="D25" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>171</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C26" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A26">
-        <v>4</v>
-      </c>
-      <c r="B26" s="3" t="s">
+      <c r="D26" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>171</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C27" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A27">
-        <v>4</v>
-      </c>
-      <c r="B27" s="3" t="s">
+      <c r="D27" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>171</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C28" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A28">
-        <v>4</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="D28" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>171</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C29" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A29">
-        <v>4</v>
-      </c>
-      <c r="B29" s="3" t="s">
+      <c r="D29" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>171</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C30" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A30">
-        <v>4</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="D30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C31" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A31">
-        <v>4</v>
-      </c>
-      <c r="B31" s="3" t="s">
+      <c r="D31" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>171</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C32" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A32">
-        <v>4</v>
-      </c>
-      <c r="B32" s="3" t="s">
+      <c r="D32" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>171</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C33" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A33">
-        <v>4</v>
-      </c>
-      <c r="B33" s="3" t="s">
+      <c r="D33" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>172</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C34" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A34">
-        <v>5</v>
-      </c>
-      <c r="B34" s="3" t="s">
+      <c r="D34" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>172</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C35" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A35">
-        <v>5</v>
-      </c>
-      <c r="B35" s="3" t="s">
+      <c r="D35" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>172</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C36" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A36">
-        <v>5</v>
-      </c>
-      <c r="B36" s="3" t="s">
+      <c r="D36" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>172</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C37" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A37">
-        <v>5</v>
-      </c>
-      <c r="B37" s="3" t="s">
+      <c r="D37" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>172</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C38" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A38">
-        <v>5</v>
-      </c>
-      <c r="B38" s="3" t="s">
+      <c r="D38" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>172</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C39" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A39">
-        <v>5</v>
-      </c>
-      <c r="B39" s="3" t="s">
+      <c r="D39" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>172</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C40" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A40">
-        <v>5</v>
-      </c>
-      <c r="B40" s="3" t="s">
+      <c r="D40" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>172</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C41" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A41">
-        <v>5</v>
-      </c>
-      <c r="B41" s="3" t="s">
+      <c r="D41" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>172</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C42" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A42">
-        <v>5</v>
-      </c>
-      <c r="B42" s="3" t="s">
+      <c r="D42" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>172</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C43" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A43">
-        <v>5</v>
-      </c>
-      <c r="B43" s="3" t="s">
+      <c r="D43" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>173</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C44" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A44">
-        <v>6</v>
-      </c>
-      <c r="B44" s="3" t="s">
+      <c r="D44" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>173</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C45" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A45">
-        <v>6</v>
-      </c>
-      <c r="B45" s="3" t="s">
+      <c r="D45" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>174</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C46" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A46">
-        <v>7</v>
-      </c>
-      <c r="B46" s="3" t="s">
+      <c r="D46" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>174</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C47" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A47">
-        <v>7</v>
-      </c>
-      <c r="B47" s="3" t="s">
+      <c r="D47" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>174</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C48" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A48">
-        <v>7</v>
-      </c>
-      <c r="B48" s="3" t="s">
+      <c r="D48" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>174</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C49" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A49">
-        <v>7</v>
-      </c>
-      <c r="B49" s="3" t="s">
+      <c r="D49" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>174</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C50" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A50">
-        <v>7</v>
-      </c>
-      <c r="B50" s="3" t="s">
+      <c r="D50" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>174</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C51" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A51">
-        <v>7</v>
-      </c>
-      <c r="B51" s="3" t="s">
+      <c r="D51" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>174</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C52" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A52">
-        <v>7</v>
-      </c>
-      <c r="B52" s="3" t="s">
+      <c r="D52" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>174</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C53" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A53">
-        <v>7</v>
-      </c>
-      <c r="B53" s="3" t="s">
+      <c r="D53" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>175</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C54" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A54">
-        <v>8</v>
-      </c>
-      <c r="B54" s="3" t="s">
+      <c r="D54" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>175</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C55" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A55">
-        <v>8</v>
-      </c>
-      <c r="B55" s="3" t="s">
+      <c r="D55" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>175</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C56" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A56">
-        <v>8</v>
-      </c>
-      <c r="B56" s="3" t="s">
+      <c r="D56" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>175</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C57" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A57">
-        <v>8</v>
-      </c>
-      <c r="B57" s="3" t="s">
+      <c r="D57" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>175</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C58" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A58">
-        <v>8</v>
-      </c>
-      <c r="B58" s="3" t="s">
+      <c r="D58" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>175</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C59" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A59">
-        <v>8</v>
-      </c>
-      <c r="B59" s="3" t="s">
+      <c r="D59" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>175</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C60" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A60">
-        <v>8</v>
-      </c>
-      <c r="B60" s="3" t="s">
+      <c r="D60" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>176</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C61" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A61">
-        <v>9</v>
-      </c>
-      <c r="B61" s="3" t="s">
+      <c r="D61" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>176</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C62" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A62">
-        <v>9</v>
-      </c>
-      <c r="B62" s="3" t="s">
+      <c r="D62" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>176</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C63" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A63">
-        <v>9</v>
-      </c>
-      <c r="B63" s="3" t="s">
+      <c r="D63" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>176</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C64" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A64">
-        <v>9</v>
-      </c>
-      <c r="B64" s="3" t="s">
+      <c r="D64" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>176</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C65" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A65">
-        <v>9</v>
-      </c>
-      <c r="B65" s="3" t="s">
+      <c r="D65" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>176</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C66" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A66">
-        <v>9</v>
-      </c>
-      <c r="B66" s="3" t="s">
+      <c r="D66" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>176</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C67" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A67">
-        <v>9</v>
-      </c>
-      <c r="B67" s="3" t="s">
+      <c r="D67" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>176</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C68" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A68">
-        <v>9</v>
-      </c>
-      <c r="B68" s="3" t="s">
+      <c r="D68" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>176</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C69" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A69">
-        <v>9</v>
-      </c>
-      <c r="B69" s="3" t="s">
+      <c r="D69" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>176</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C70" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A70">
-        <v>9</v>
-      </c>
-      <c r="B70" s="3" t="s">
+      <c r="D70" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>176</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C71" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A71">
-        <v>9</v>
-      </c>
-      <c r="B71" s="3" t="s">
+      <c r="D71" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>176</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C72" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A72">
-        <v>9</v>
-      </c>
-      <c r="B72" s="3" t="s">
+      <c r="D72" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>176</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C73" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A73">
-        <v>9</v>
-      </c>
-      <c r="B73" s="3" t="s">
+      <c r="D73" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>176</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C74" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A74">
-        <v>9</v>
-      </c>
-      <c r="B74" s="3" t="s">
+      <c r="D74" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>176</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C75" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A75">
-        <v>9</v>
-      </c>
-      <c r="B75" s="3" t="s">
+      <c r="D75" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C76" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A76">
-        <v>9</v>
-      </c>
-      <c r="B76" s="3" t="s">
+      <c r="D76" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>177</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C77" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A77">
-        <v>10</v>
-      </c>
-      <c r="B77" s="3" t="s">
+      <c r="D77" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>177</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C78" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A78">
-        <v>10</v>
-      </c>
-      <c r="B78" s="3" t="s">
+      <c r="D78" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A79" t="s">
+        <v>177</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C79" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A79">
-        <v>10</v>
-      </c>
-      <c r="B79" s="3" t="s">
+      <c r="D79" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A80" t="s">
+        <v>177</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C80" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A80">
-        <v>10</v>
-      </c>
-      <c r="B80" s="3" t="s">
+      <c r="D80" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A81" t="s">
+        <v>177</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C81" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A81">
-        <v>10</v>
-      </c>
-      <c r="B81" s="3" t="s">
+      <c r="D81" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A82" t="s">
+        <v>177</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C82" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A82">
-        <v>10</v>
-      </c>
-      <c r="B82" s="3" t="s">
+      <c r="D82" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A83" t="s">
+        <v>177</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C83" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A83">
-        <v>10</v>
-      </c>
-      <c r="B83" s="3" t="s">
+      <c r="D83" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A84" t="s">
+        <v>177</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C84" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A84">
-        <v>10</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C84" t="s">
-        <v>167</v>
+      <c r="D84" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>